--- a/artfynd/A 22291-2025 artfynd.xlsx
+++ b/artfynd/A 22291-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017204</v>
       </c>
       <c r="B2" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017206</v>
       </c>
       <c r="B3" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017207</v>
       </c>
       <c r="B4" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22291-2025 artfynd.xlsx
+++ b/artfynd/A 22291-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017204</v>
       </c>
       <c r="B2" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017206</v>
       </c>
       <c r="B3" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017207</v>
       </c>
       <c r="B4" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22291-2025 artfynd.xlsx
+++ b/artfynd/A 22291-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017204</v>
       </c>
       <c r="B2" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017206</v>
       </c>
       <c r="B3" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017207</v>
       </c>
       <c r="B4" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22291-2025 artfynd.xlsx
+++ b/artfynd/A 22291-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017204</v>
       </c>
       <c r="B2" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017206</v>
       </c>
       <c r="B3" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017207</v>
       </c>
       <c r="B4" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22291-2025 artfynd.xlsx
+++ b/artfynd/A 22291-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -991,6 +991,112 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128533118</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92742</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bunkris, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>413094</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6808121</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22291-2025 artfynd.xlsx
+++ b/artfynd/A 22291-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128533118</v>
       </c>
       <c r="B5" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22291-2025 artfynd.xlsx
+++ b/artfynd/A 22291-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128533118</v>
       </c>
       <c r="B5" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22291-2025 artfynd.xlsx
+++ b/artfynd/A 22291-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128533118</v>
       </c>
       <c r="B5" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22291-2025 artfynd.xlsx
+++ b/artfynd/A 22291-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128533118</v>
       </c>
       <c r="B5" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22291-2025 artfynd.xlsx
+++ b/artfynd/A 22291-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128533118</v>
       </c>
       <c r="B5" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22291-2025 artfynd.xlsx
+++ b/artfynd/A 22291-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128533118</v>
       </c>
       <c r="B5" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22291-2025 artfynd.xlsx
+++ b/artfynd/A 22291-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128533118</v>
       </c>
       <c r="B5" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22291-2025 artfynd.xlsx
+++ b/artfynd/A 22291-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128533118</v>
       </c>
       <c r="B5" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22291-2025 artfynd.xlsx
+++ b/artfynd/A 22291-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128533118</v>
       </c>
       <c r="B5" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22291-2025 artfynd.xlsx
+++ b/artfynd/A 22291-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128533118</v>
       </c>
       <c r="B5" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22291-2025 artfynd.xlsx
+++ b/artfynd/A 22291-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>128533118</v>
       </c>
       <c r="B5" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22291-2025 artfynd.xlsx
+++ b/artfynd/A 22291-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533118</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017207</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017204</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,8 +1116,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017206</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>